--- a/assets/data/output/attendance.xlsx
+++ b/assets/data/output/attendance.xlsx
@@ -456,7 +456,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46124</v>
+        <v>46150</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -470,7 +470,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-12 09:24:17</t>
+          <t>2026-05-08 08:49:40</t>
         </is>
       </c>
     </row>
